--- a/outputs/unit_economics/юнитка_план_продаж_ROI30_факт_цены.xlsx
+++ b/outputs/unit_economics/юнитка_план_продаж_ROI30_факт_цены.xlsx
@@ -520,14 +520,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПЛАН ПРОДАЖ ПОД ОСТАТКИ — ROI ≥ 30% (на фактических ценах и СПП, база Москва Центр)</t>
+          <t>ПЛАН ПРОДАЖ ПОД ОСТАТКИ — ROI ≥ 30% (факт. цены и СПП, база Москва Центр)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Цены и СПП — из твоего файла (Москва Центр). Себес — по последнему приходу. Комиссия 41,5% (шампуни 38%), эквайринг 2,35%, налог 6%, ДРР 10%, логистика 90₽, выкуп 92%. ROI≥30% — цена сохранена; &lt;30% — поднята до 30%.</t>
+          <t>Цены/СПП из твоего файла (Москва Центр). Себес — по последнему приходу. Комиссия 41,5% (шампуни 38%), эквайринг 2,35%, налог 6%, ДРР 10%, логистика 90₽, выкуп 92%. ROI≥30% — цена сохранена; &lt;30% — поднята до 30%.</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
         <v>437190353</v>
       </c>
       <c r="C121" s="12" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="D121" s="11" t="n">
         <v>102</v>
@@ -4876,25 +4876,25 @@
         <v>2946</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>239</v>
+        <v>3710</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>159</v>
+        <v>2475</v>
       </c>
       <c r="I121" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J121" s="11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>0</v>
+        <v>33445</v>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="B125" s="9" t="n"/>
       <c r="C125" s="10" t="n">
-        <v>3554019</v>
+        <v>3665505</v>
       </c>
       <c r="D125" s="10" t="n">
         <v>7609</v>
@@ -5058,7 +5058,7 @@
       <c r="J125" s="9" t="n"/>
       <c r="K125" s="9" t="n"/>
       <c r="L125" s="10" t="n">
-        <v>1295882</v>
+        <v>1329327</v>
       </c>
       <c r="M125" s="9" t="n"/>
     </row>
@@ -5270,7 +5270,7 @@
         <v>248929125</v>
       </c>
       <c r="C132" s="12" t="n">
-        <v>0</v>
+        <v>1057</v>
       </c>
       <c r="D132" s="11" t="n">
         <v>55</v>
@@ -5279,25 +5279,25 @@
         <v>3257</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>239</v>
+        <v>3597</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>159</v>
+        <v>2399</v>
       </c>
       <c r="I132" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J132" s="11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K132" s="12" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>0</v>
+        <v>17444</v>
       </c>
       <c r="M132" s="11" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B133" s="9" t="n"/>
       <c r="C133" s="10" t="n">
-        <v>288750</v>
+        <v>346885</v>
       </c>
       <c r="D133" s="10" t="n">
         <v>580</v>
@@ -5326,7 +5326,7 @@
       <c r="J133" s="9" t="n"/>
       <c r="K133" s="9" t="n"/>
       <c r="L133" s="10" t="n">
-        <v>86579</v>
+        <v>104023</v>
       </c>
       <c r="M133" s="9" t="n"/>
     </row>
@@ -6032,7 +6032,7 @@
         <v>1119249556</v>
       </c>
       <c r="C152" s="12" t="n">
-        <v>0</v>
+        <v>1336</v>
       </c>
       <c r="D152" s="11" t="n">
         <v>1008</v>
@@ -6041,25 +6041,25 @@
         <v>3591</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>239</v>
+        <v>4482</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>159</v>
+        <v>2989</v>
       </c>
       <c r="I152" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J152" s="11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K152" s="12" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>0</v>
+        <v>403991</v>
       </c>
       <c r="M152" s="11" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B154" s="9" t="n"/>
       <c r="C154" s="10" t="n">
-        <v>386678</v>
+        <v>1733366</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>1405</v>
@@ -6133,7 +6133,7 @@
       <c r="J154" s="9" t="n"/>
       <c r="K154" s="9" t="n"/>
       <c r="L154" s="10" t="n">
-        <v>116008</v>
+        <v>519999</v>
       </c>
       <c r="M154" s="9" t="n"/>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B156" s="14" t="n"/>
       <c r="C156" s="15" t="n">
-        <v>45942101</v>
+        <v>47458410</v>
       </c>
       <c r="D156" s="15" t="n">
         <v>107901</v>
@@ -6158,14 +6158,14 @@
       <c r="J156" s="14" t="n"/>
       <c r="K156" s="14" t="n"/>
       <c r="L156" s="15" t="n">
-        <v>18869524</v>
+        <v>19324404</v>
       </c>
       <c r="M156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="16" t="inlineStr">
         <is>
-          <t>Себес остатков: 45.94 млн ₽  |  Заработок при ROI≥30%: 18.87 млн ₽  |  Остаток: 107,901 шт  |  Позиций поднять цену: 47 из 99</t>
+          <t>Себес остатков: 47.46 млн ₽  |  Заработок при ROI≥30%: 19.32 млн ₽  |  Остаток: 107,901 шт  |  Поднять цену: 47 из 99</t>
         </is>
       </c>
     </row>

--- a/outputs/unit_economics/юнитка_план_продаж_ROI30_факт_цены.xlsx
+++ b/outputs/unit_economics/юнитка_план_продаж_ROI30_факт_цены.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="План ROI30 (факт цены)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="План ROI30 (факт ставки)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,35 +499,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПЛАН ПРОДАЖ ПОД ОСТАТКИ — ROI ≥ 30% (факт. цены и СПП, база Москва Центр)</t>
+          <t>ПЛАН ПРОДАЖ ПОД ОСТАТКИ — ROI ≥ 30% (факт. цены, СПП и ставки Ракеты)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Цены/СПП из твоего файла (Москва Центр). Себес — по последнему приходу. Комиссия 41,5% (шампуни 38%), эквайринг 2,35%, налог 6%, ДРР 10%, логистика 90₽, выкуп 92%. ROI≥30% — цена сохранена; &lt;30% — поднята до 30%.</t>
+          <t>Цены/СПП — твой файл (Москва Центр). Комиссия+эквайринг, доставка, налог — ФАКТ Ракеты по каждому SKU (31.08–27.09.2026). ДРР 10%. ROI≥30% — цена сохранена; &lt;30% — поднята до 30%.</t>
         </is>
       </c>
     </row>
@@ -579,20 +581,30 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>Ком+экв %</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Доставка ₽</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>Новый ROI %</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Маржа ₽/ед</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Заработок ₽</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
@@ -616,6 +628,8 @@
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n"/>
       <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -636,7 +650,7 @@
         <v>1387</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1387</v>
@@ -648,15 +662,21 @@
         <v>33.3</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>37</v>
+        <v>45.2</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>126</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>27487</v>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>141</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>30763</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -682,10 +702,12 @@
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="9" t="n"/>
-      <c r="L8" s="10" t="n">
-        <v>27487</v>
-      </c>
+      <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
+      <c r="N8" s="10" t="n">
+        <v>30763</v>
+      </c>
+      <c r="O8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -705,6 +727,8 @@
       <c r="K9" s="5" t="n"/>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -725,7 +749,7 @@
         <v>1387</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1387</v>
@@ -737,15 +761,21 @@
         <v>33.4</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>92</v>
+        <v>40.3</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>249</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>14668</v>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
+        <v>112</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>229</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>13530</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -770,7 +800,7 @@
         <v>1387</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1387</v>
@@ -782,15 +812,21 @@
         <v>33.3</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>65</v>
+        <v>40.7</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>204</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>2240</v>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
+        <v>134</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>1755</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -815,7 +851,7 @@
         <v>920</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>920</v>
@@ -827,15 +863,21 @@
         <v>33.4</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>106</v>
+        <v>40.7</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>160</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>47474</v>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>52402</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -861,10 +903,12 @@
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
-      <c r="L13" s="10" t="n">
-        <v>64382</v>
-      </c>
+      <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
+      <c r="N13" s="10" t="n">
+        <v>67687</v>
+      </c>
+      <c r="O13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -884,6 +928,8 @@
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -904,7 +950,7 @@
         <v>2945</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>2945</v>
@@ -916,15 +962,21 @@
         <v>33.3</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>67</v>
+        <v>40.9</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>484</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>191126</v>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
+        <v>207</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>140025</v>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -950,10 +1002,12 @@
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="9" t="n"/>
-      <c r="L16" s="10" t="n">
-        <v>191126</v>
-      </c>
+      <c r="L16" s="9" t="n"/>
       <c r="M16" s="9" t="n"/>
+      <c r="N16" s="10" t="n">
+        <v>140025</v>
+      </c>
+      <c r="O16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -973,6 +1027,8 @@
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -993,7 +1049,7 @@
         <v>1076</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1076</v>
@@ -1005,15 +1061,21 @@
         <v>33.4</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>41</v>
+        <v>43.7</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>34137</v>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
+        <v>68</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>43939</v>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1038,7 +1100,7 @@
         <v>1855</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1855</v>
@@ -1050,15 +1112,21 @@
         <v>33.4</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>48</v>
+        <v>44.2</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>214</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>10694</v>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>242</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>12078</v>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1084,10 +1152,12 @@
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="9" t="n"/>
-      <c r="L20" s="10" t="n">
-        <v>44831</v>
-      </c>
+      <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n"/>
+      <c r="N20" s="10" t="n">
+        <v>56017</v>
+      </c>
+      <c r="O20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1107,6 +1177,8 @@
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1127,7 +1199,7 @@
         <v>921</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>921</v>
@@ -1139,62 +1211,74 @@
         <v>33.3</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>73</v>
+        <v>44.2</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>118</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <v>754321</v>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>997272</v>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Антивозрастной отбеливающий крем с коллагеном</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="6" t="n">
         <v>238416010</v>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="7" t="n">
         <v>184</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="6" t="n">
         <v>254</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="7" t="n">
         <v>766</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>823</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>548</v>
-      </c>
-      <c r="I23" s="11" t="n">
+      <c r="F23" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>766</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>510</v>
+      </c>
+      <c r="I23" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="J23" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>14012</v>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="J23" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>17388</v>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1301,7 @@
         <v>1233</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1233</v>
@@ -1229,15 +1313,21 @@
         <v>33.3</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>88</v>
+        <v>44.2</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>190</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>10092</v>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>221</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>11703</v>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1262,7 +1352,7 @@
         <v>1233</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1233</v>
@@ -1274,15 +1364,21 @@
         <v>33.3</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>68</v>
+        <v>44.2</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>164</v>
-      </c>
-      <c r="L25" s="7" t="n">
-        <v>32470</v>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>195</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>38513</v>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1307,7 +1403,7 @@
         <v>1076</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1076</v>
@@ -1319,62 +1415,74 @@
         <v>33.4</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>39</v>
+        <v>44.2</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>67888</v>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>95945</v>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональный крем с муцином улитки 21 тон</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="6" t="n">
         <v>207796898</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="7" t="n">
         <v>271</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="7" t="n">
         <v>1077</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>1099</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>733</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>32497</v>
-      </c>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F27" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>41577</v>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1505,7 @@
         <v>1076</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1076</v>
@@ -1409,15 +1517,21 @@
         <v>33.3</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>53</v>
+        <v>44.2</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>119</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>1431</v>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>1789</v>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1442,7 +1556,7 @@
         <v>1387</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1387</v>
@@ -1454,107 +1568,125 @@
         <v>33.4</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>54</v>
+        <v>44.2</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>165</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>3799</v>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>203</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>4667</v>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 13] / Тональный крем с частичками золота 13 тон</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="6" t="n">
         <v>170198180</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="7" t="n">
         <v>270</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="7" t="n">
         <v>1077</v>
       </c>
-      <c r="F30" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>1095</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>731</v>
-      </c>
-      <c r="I30" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>16179</v>
-      </c>
-      <c r="M30" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F30" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>1077</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>23261</v>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [Tone 21] / Тональный крем с частичками золота 21 тон</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="6" t="n">
         <v>170198109</v>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="7" t="n">
         <v>270</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="7" t="n">
         <v>1076</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>1095</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>731</v>
-      </c>
-      <c r="I31" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>32358</v>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F31" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>718</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>45630</v>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -1577,27 +1709,33 @@
         <v>1076</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1241</v>
+        <v>1163</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>828</v>
+        <v>776</v>
       </c>
       <c r="I32" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J32" s="11" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L32" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>94635</v>
       </c>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="O32" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -1622,7 +1760,7 @@
         <v>1233</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1233</v>
@@ -1634,15 +1772,21 @@
         <v>33.3</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>122</v>
+        <v>44.1</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>224</v>
-      </c>
-      <c r="L33" s="7" t="n">
-        <v>78719</v>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>94865</v>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1667,7 +1811,7 @@
         <v>1233</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1233</v>
@@ -1679,15 +1823,21 @@
         <v>33.3</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>122</v>
+        <v>44.2</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>224</v>
-      </c>
-      <c r="L34" s="7" t="n">
-        <v>120538</v>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>269</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>145105</v>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1712,7 +1862,7 @@
         <v>1233</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1233</v>
@@ -1724,62 +1874,74 @@
         <v>33.3</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>122</v>
+        <v>44.2</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>224</v>
-      </c>
-      <c r="L35" s="7" t="n">
-        <v>155201</v>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>252</v>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>174950</v>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увлажняющий BB крем с коллагеном</t>
         </is>
       </c>
-      <c r="B36" s="11" t="n">
+      <c r="B36" s="6" t="n">
         <v>238413828</v>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="6" t="n">
         <v>687</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="7" t="n">
         <v>792</v>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>840</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>559</v>
-      </c>
-      <c r="I36" s="11" t="n">
+      <c r="F36" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>792</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>527</v>
+      </c>
+      <c r="I36" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="J36" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>39009</v>
-      </c>
-      <c r="M36" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="J36" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>47582</v>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -1803,10 +1965,12 @@
       <c r="I37" s="9" t="n"/>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="9" t="n"/>
-      <c r="L37" s="10" t="n">
-        <v>1453149</v>
-      </c>
+      <c r="L37" s="9" t="n"/>
       <c r="M37" s="9" t="n"/>
+      <c r="N37" s="10" t="n">
+        <v>1834882</v>
+      </c>
+      <c r="O37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1826,6 +1990,8 @@
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="n"/>
       <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -1846,7 +2012,7 @@
         <v>1542</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1542</v>
@@ -1858,15 +2024,21 @@
         <v>33.3</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>48</v>
+        <v>44.3</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>172</v>
-      </c>
-      <c r="L39" s="7" t="n">
-        <v>1237630</v>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="L39" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>211</v>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>1518306</v>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1891,7 +2063,7 @@
         <v>1232</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1232</v>
@@ -1903,15 +2075,21 @@
         <v>33.4</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>39</v>
+        <v>44.2</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>114</v>
-      </c>
-      <c r="L40" s="7" t="n">
-        <v>7271</v>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="L40" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>9365</v>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -1935,24 +2113,30 @@
       <c r="E41" s="12" t="n"/>
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="12" t="n">
-        <v>1478</v>
+        <v>1472</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="I41" s="11" t="n">
         <v>33</v>
       </c>
       <c r="J41" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="L41" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>234</v>
       </c>
-      <c r="M41" s="11" t="inlineStr">
+      <c r="O41" s="11" t="inlineStr">
         <is>
           <t>Поднять до ROI30 (нет цены)</t>
         </is>
@@ -1978,10 +2162,12 @@
       <c r="I42" s="9" t="n"/>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
-      <c r="L42" s="10" t="n">
-        <v>1245135</v>
-      </c>
+      <c r="L42" s="9" t="n"/>
       <c r="M42" s="9" t="n"/>
+      <c r="N42" s="10" t="n">
+        <v>1527905</v>
+      </c>
+      <c r="O42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -2001,6 +2187,8 @@
       <c r="K43" s="5" t="n"/>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2021,7 +2209,7 @@
         <v>1515</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1515</v>
@@ -2033,15 +2221,21 @@
         <v>33.3</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>50</v>
+        <v>44.2</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="L44" s="7" t="n">
-        <v>1058947</v>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="L44" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>208</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>1260595</v>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2066,7 +2260,7 @@
         <v>1620</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1620</v>
@@ -2078,15 +2272,21 @@
         <v>33.3</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>57</v>
+        <v>40.7</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>225</v>
-      </c>
-      <c r="L45" s="7" t="n">
-        <v>720836</v>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
+        <v>136</v>
+      </c>
+      <c r="L45" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>561178</v>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2111,7 +2311,7 @@
         <v>2166</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>2166</v>
@@ -2123,62 +2323,74 @@
         <v>33.3</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>83</v>
+        <v>44.2</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>358</v>
-      </c>
-      <c r="L46" s="7" t="n">
-        <v>304780</v>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="L46" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>396</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>337247</v>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с муцином королевской улитки</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B47" s="6" t="n">
         <v>169076150</v>
       </c>
-      <c r="C47" s="12" t="n">
+      <c r="C47" s="7" t="n">
         <v>314</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="6" t="n">
         <v>835</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="7" t="n">
         <v>1233</v>
       </c>
-      <c r="F47" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="G47" s="12" t="n">
-        <v>1236</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>824</v>
-      </c>
-      <c r="I47" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K47" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>78617</v>
-      </c>
-      <c r="M47" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F47" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>1233</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>822</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="L47" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>111380</v>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -2201,27 +2413,33 @@
         <v>1387</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1479</v>
+        <v>1403</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>987</v>
+        <v>936</v>
       </c>
       <c r="I48" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J48" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K48" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L48" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="N48" s="12" t="n">
         <v>96170</v>
       </c>
-      <c r="M48" s="11" t="inlineStr">
+      <c r="O48" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -2246,7 +2464,7 @@
         <v>1543</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1543</v>
@@ -2258,15 +2476,21 @@
         <v>33.3</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>47</v>
+        <v>40.7</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>187</v>
-      </c>
-      <c r="L49" s="7" t="n">
-        <v>429745</v>
-      </c>
-      <c r="M49" s="6" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="L49" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>172</v>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>394789</v>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2291,7 +2515,7 @@
         <v>1543</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1543</v>
@@ -2303,15 +2527,21 @@
         <v>33.3</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>48</v>
+        <v>41.2</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>191</v>
-      </c>
-      <c r="L50" s="7" t="n">
-        <v>644596</v>
-      </c>
-      <c r="M50" s="6" t="inlineStr">
+        <v>84</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="M50" s="7" t="n">
+        <v>179</v>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>605425</v>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2336,7 +2566,7 @@
         <v>1076</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1076</v>
@@ -2348,15 +2578,21 @@
         <v>33.3</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>48</v>
+        <v>44.3</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="L51" s="7" t="n">
-        <v>17297</v>
-      </c>
-      <c r="M51" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>23543</v>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2381,7 +2617,7 @@
         <v>2010</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>2010</v>
@@ -2393,15 +2629,21 @@
         <v>33.3</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>240</v>
-      </c>
-      <c r="L52" s="7" t="n">
-        <v>57479</v>
-      </c>
-      <c r="M52" s="6" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="M52" s="7" t="n">
+        <v>271</v>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>64837</v>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2426,7 +2668,7 @@
         <v>920</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>920</v>
@@ -2438,15 +2680,21 @@
         <v>33.4</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>73</v>
+        <v>44.6</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>117</v>
-      </c>
-      <c r="L53" s="7" t="n">
-        <v>44811</v>
-      </c>
-      <c r="M53" s="6" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="L53" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="N53" s="7" t="n">
+        <v>57883</v>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2472,10 +2720,12 @@
       <c r="I54" s="9" t="n"/>
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
-      <c r="L54" s="10" t="n">
-        <v>3453278</v>
-      </c>
+      <c r="L54" s="9" t="n"/>
       <c r="M54" s="9" t="n"/>
+      <c r="N54" s="10" t="n">
+        <v>3513047</v>
+      </c>
+      <c r="O54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -2495,6 +2745,8 @@
       <c r="K55" s="5" t="n"/>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -2515,27 +2767,33 @@
         <v>2477</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>2686</v>
+        <v>2661</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1792</v>
+        <v>1775</v>
       </c>
       <c r="I56" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J56" s="11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L56" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K56" s="12" t="n">
+      <c r="M56" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="L56" s="12" t="n">
+      <c r="N56" s="12" t="n">
         <v>214964</v>
       </c>
-      <c r="M56" s="11" t="inlineStr">
+      <c r="O56" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -2561,10 +2819,12 @@
       <c r="I57" s="9" t="n"/>
       <c r="J57" s="9" t="n"/>
       <c r="K57" s="9" t="n"/>
-      <c r="L57" s="10" t="n">
+      <c r="L57" s="9" t="n"/>
+      <c r="M57" s="9" t="n"/>
+      <c r="N57" s="10" t="n">
         <v>214964</v>
       </c>
-      <c r="M57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2584,6 +2844,8 @@
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
       <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -2604,7 +2866,7 @@
         <v>921</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>921</v>
@@ -2616,62 +2878,74 @@
         <v>33.3</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>38</v>
+        <v>44.2</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L59" s="7" t="n">
-        <v>548937</v>
-      </c>
-      <c r="M59" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="M59" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="N59" s="7" t="n">
+        <v>844158</v>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажняющий антивозрастной с муцином улитки</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B60" s="6" t="n">
         <v>207483179</v>
       </c>
-      <c r="C60" s="12" t="n">
+      <c r="C60" s="7" t="n">
         <v>186</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="6" t="n">
         <v>777</v>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="E60" s="7" t="n">
         <v>766</v>
       </c>
-      <c r="F60" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G60" s="12" t="n">
-        <v>829</v>
-      </c>
-      <c r="H60" s="12" t="n">
-        <v>552</v>
-      </c>
-      <c r="I60" s="11" t="n">
+      <c r="F60" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>766</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>510</v>
+      </c>
+      <c r="I60" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="J60" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>43324</v>
-      </c>
-      <c r="M60" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="J60" s="6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="M60" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="N60" s="7" t="n">
+        <v>56306</v>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2968,7 @@
         <v>920</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>920</v>
@@ -2706,15 +2980,21 @@
         <v>33.4</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>38</v>
+        <v>44.1</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L61" s="7" t="n">
-        <v>122255</v>
-      </c>
-      <c r="M61" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="M61" s="7" t="n">
+        <v>123</v>
+      </c>
+      <c r="N61" s="7" t="n">
+        <v>197292</v>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2740,10 +3020,12 @@
       <c r="I62" s="9" t="n"/>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="9" t="n"/>
-      <c r="L62" s="10" t="n">
-        <v>714516</v>
-      </c>
+      <c r="L62" s="9" t="n"/>
       <c r="M62" s="9" t="n"/>
+      <c r="N62" s="10" t="n">
+        <v>1097756</v>
+      </c>
+      <c r="O62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -2763,6 +3045,8 @@
       <c r="K63" s="5" t="n"/>
       <c r="L63" s="5" t="n"/>
       <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -2783,7 +3067,7 @@
         <v>1387</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1387</v>
@@ -2795,15 +3079,21 @@
         <v>33.3</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>136</v>
-      </c>
-      <c r="L64" s="7" t="n">
-        <v>176888</v>
-      </c>
-      <c r="M64" s="6" t="inlineStr">
+        <v>114</v>
+      </c>
+      <c r="L64" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="M64" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="N64" s="7" t="n">
+        <v>200279</v>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2829,10 +3119,12 @@
       <c r="I65" s="9" t="n"/>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="9" t="n"/>
-      <c r="L65" s="10" t="n">
-        <v>176888</v>
-      </c>
+      <c r="L65" s="9" t="n"/>
       <c r="M65" s="9" t="n"/>
+      <c r="N65" s="10" t="n">
+        <v>200279</v>
+      </c>
+      <c r="O65" s="9" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -2852,6 +3144,8 @@
       <c r="K66" s="5" t="n"/>
       <c r="L66" s="5" t="n"/>
       <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -2872,7 +3166,7 @@
         <v>1232</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1232</v>
@@ -2884,15 +3178,21 @@
         <v>33.4</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>53</v>
+        <v>44.2</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>141</v>
-      </c>
-      <c r="L67" s="7" t="n">
-        <v>160044</v>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="L67" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="M67" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="N67" s="7" t="n">
+        <v>177931</v>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2917,7 +3217,7 @@
         <v>1232</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1232</v>
@@ -2929,15 +3229,21 @@
         <v>33.4</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>53</v>
+        <v>44.2</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>141</v>
-      </c>
-      <c r="L68" s="7" t="n">
-        <v>167241</v>
-      </c>
-      <c r="M68" s="6" t="inlineStr">
+        <v>120</v>
+      </c>
+      <c r="L68" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="M68" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="N68" s="7" t="n">
+        <v>132363</v>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -2962,7 +3268,7 @@
         <v>1232</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1232</v>
@@ -2974,62 +3280,74 @@
         <v>33.4</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>53</v>
+        <v>44.2</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>141</v>
-      </c>
-      <c r="L69" s="7" t="n">
-        <v>31331</v>
-      </c>
-      <c r="M69" s="6" t="inlineStr">
+        <v>65</v>
+      </c>
+      <c r="L69" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="M69" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="N69" s="7" t="n">
+        <v>36539</v>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для лица увлажняющий с экстрактом алоэ</t>
         </is>
       </c>
-      <c r="B70" s="11" t="n">
+      <c r="B70" s="6" t="n">
         <v>212759698</v>
       </c>
-      <c r="C70" s="12" t="n">
+      <c r="C70" s="7" t="n">
         <v>265</v>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D70" s="6" t="n">
         <v>202</v>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="E70" s="7" t="n">
         <v>1076</v>
       </c>
-      <c r="F70" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>1082</v>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="I70" s="11" t="n">
+      <c r="F70" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>717</v>
+      </c>
+      <c r="I70" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="J70" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="L70" s="12" t="n">
-        <v>16081</v>
-      </c>
-      <c r="M70" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="J70" s="6" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L70" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="M70" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="N70" s="7" t="n">
+        <v>18953</v>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -3053,10 +3371,12 @@
       <c r="I71" s="9" t="n"/>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="9" t="n"/>
-      <c r="L71" s="10" t="n">
-        <v>374697</v>
-      </c>
+      <c r="L71" s="9" t="n"/>
       <c r="M71" s="9" t="n"/>
+      <c r="N71" s="10" t="n">
+        <v>365786</v>
+      </c>
+      <c r="O71" s="9" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -3076,49 +3396,57 @@
       <c r="K72" s="5" t="n"/>
       <c r="L72" s="5" t="n"/>
       <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>JMSOLUTION - MASK PACK BLACK [30ml*10ea] - ассорти набор 10шт в упаковке</t>
         </is>
       </c>
-      <c r="B73" s="11" t="n">
+      <c r="B73" s="6" t="n">
         <v>214977901</v>
       </c>
-      <c r="C73" s="12" t="n">
+      <c r="C73" s="7" t="n">
         <v>463</v>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="6" t="n">
         <v>980</v>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="E73" s="7" t="n">
         <v>1699</v>
       </c>
-      <c r="F73" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>1710</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>1141</v>
-      </c>
-      <c r="I73" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J73" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>139</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>136181</v>
-      </c>
-      <c r="M73" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F73" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>1699</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>1133</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>171348</v>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -3142,10 +3470,12 @@
       <c r="I74" s="9" t="n"/>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="9" t="n"/>
-      <c r="L74" s="10" t="n">
-        <v>136181</v>
-      </c>
+      <c r="L74" s="9" t="n"/>
       <c r="M74" s="9" t="n"/>
+      <c r="N74" s="10" t="n">
+        <v>171348</v>
+      </c>
+      <c r="O74" s="9" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3165,6 +3495,8 @@
       <c r="K75" s="5" t="n"/>
       <c r="L75" s="5" t="n"/>
       <c r="M75" s="5" t="n"/>
+      <c r="N75" s="5" t="n"/>
+      <c r="O75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -3185,7 +3517,7 @@
         <v>2010</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>2010</v>
@@ -3197,15 +3529,21 @@
         <v>33.3</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>57</v>
+        <v>41.4</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>262</v>
-      </c>
-      <c r="L76" s="7" t="n">
-        <v>217750</v>
-      </c>
-      <c r="M76" s="6" t="inlineStr">
+        <v>84</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>318</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>264832</v>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3231,10 +3569,12 @@
       <c r="I77" s="9" t="n"/>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="9" t="n"/>
-      <c r="L77" s="10" t="n">
-        <v>217750</v>
-      </c>
+      <c r="L77" s="9" t="n"/>
       <c r="M77" s="9" t="n"/>
+      <c r="N77" s="10" t="n">
+        <v>264832</v>
+      </c>
+      <c r="O77" s="9" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3254,6 +3594,8 @@
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -3274,7 +3616,7 @@
         <v>765</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>765</v>
@@ -3286,15 +3628,21 @@
         <v>33.3</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>99</v>
+        <v>44.3</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="L79" s="7" t="n">
-        <v>37827</v>
-      </c>
-      <c r="M79" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L79" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>54752</v>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3320,10 +3668,12 @@
       <c r="I80" s="9" t="n"/>
       <c r="J80" s="9" t="n"/>
       <c r="K80" s="9" t="n"/>
-      <c r="L80" s="10" t="n">
-        <v>37827</v>
-      </c>
+      <c r="L80" s="9" t="n"/>
       <c r="M80" s="9" t="n"/>
+      <c r="N80" s="10" t="n">
+        <v>54752</v>
+      </c>
+      <c r="O80" s="9" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -3343,6 +3693,8 @@
       <c r="K81" s="5" t="n"/>
       <c r="L81" s="5" t="n"/>
       <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -3363,7 +3715,7 @@
         <v>764</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>764</v>
@@ -3375,15 +3727,21 @@
         <v>33.4</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>64</v>
+        <v>40.2</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="L82" s="7" t="n">
-        <v>18997</v>
-      </c>
-      <c r="M82" s="6" t="inlineStr">
+        <v>68</v>
+      </c>
+      <c r="L82" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="N82" s="7" t="n">
+        <v>31307</v>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3409,10 +3767,12 @@
       <c r="I83" s="9" t="n"/>
       <c r="J83" s="9" t="n"/>
       <c r="K83" s="9" t="n"/>
-      <c r="L83" s="10" t="n">
-        <v>18997</v>
-      </c>
+      <c r="L83" s="9" t="n"/>
       <c r="M83" s="9" t="n"/>
+      <c r="N83" s="10" t="n">
+        <v>31307</v>
+      </c>
+      <c r="O83" s="9" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -3432,6 +3792,8 @@
       <c r="K84" s="5" t="n"/>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="5" t="n"/>
+      <c r="N84" s="5" t="n"/>
+      <c r="O84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -3452,7 +3814,7 @@
         <v>4191</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>4191</v>
@@ -3464,15 +3826,21 @@
         <v>33.3</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>80</v>
+        <v>44.2</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>718</v>
-      </c>
-      <c r="L85" s="7" t="n">
-        <v>894475</v>
-      </c>
-      <c r="M85" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="M85" s="7" t="n">
+        <v>759</v>
+      </c>
+      <c r="N85" s="7" t="n">
+        <v>945494</v>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3497,7 +3865,7 @@
         <v>2789</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>2789</v>
@@ -3509,15 +3877,21 @@
         <v>33.3</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>61</v>
+        <v>44.2</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>397</v>
-      </c>
-      <c r="L86" s="7" t="n">
-        <v>253653</v>
-      </c>
-      <c r="M86" s="6" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>444</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>283826</v>
+      </c>
+      <c r="O86" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3542,27 +3916,33 @@
         <v>2166</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>2574</v>
+        <v>2499</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>1717</v>
+        <v>1667</v>
       </c>
       <c r="I87" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J87" s="11" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="L87" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K87" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="L87" s="12" t="n">
+      <c r="N87" s="12" t="n">
         <v>108095</v>
       </c>
-      <c r="M87" s="11" t="inlineStr">
+      <c r="O87" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -3587,7 +3967,7 @@
         <v>3723</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>3723</v>
@@ -3599,15 +3979,21 @@
         <v>33.3</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>67</v>
+        <v>44.3</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>573</v>
-      </c>
-      <c r="L88" s="7" t="n">
-        <v>86537</v>
-      </c>
-      <c r="M88" s="6" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="L88" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>606</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>91489</v>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3632,7 +4018,7 @@
         <v>3412</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>3412</v>
@@ -3644,15 +4030,21 @@
         <v>33.3</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>76</v>
+        <v>44.6</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>559</v>
-      </c>
-      <c r="L89" s="7" t="n">
-        <v>266587</v>
-      </c>
-      <c r="M89" s="6" t="inlineStr">
+        <v>88</v>
+      </c>
+      <c r="L89" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="M89" s="7" t="n">
+        <v>542</v>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>258423</v>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3677,7 +4069,7 @@
         <v>4503</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>4503</v>
@@ -3689,15 +4081,21 @@
         <v>33.3</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>749</v>
-      </c>
-      <c r="L90" s="7" t="n">
-        <v>451416</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
+        <v>131</v>
+      </c>
+      <c r="L90" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>690</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>415986</v>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3723,10 +4121,12 @@
       <c r="I91" s="9" t="n"/>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="9" t="n"/>
-      <c r="L91" s="10" t="n">
-        <v>2060763</v>
-      </c>
+      <c r="L91" s="9" t="n"/>
       <c r="M91" s="9" t="n"/>
+      <c r="N91" s="10" t="n">
+        <v>2103313</v>
+      </c>
+      <c r="O91" s="9" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -3746,6 +4146,8 @@
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="n"/>
       <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
@@ -3766,27 +4168,33 @@
         <v>2010</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>2364</v>
+        <v>2412</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>1577</v>
+        <v>1609</v>
       </c>
       <c r="I93" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J93" s="11" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="L93" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K93" s="12" t="n">
+      <c r="M93" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="L93" s="12" t="n">
+      <c r="N93" s="12" t="n">
         <v>21075</v>
       </c>
-      <c r="M93" s="11" t="inlineStr">
+      <c r="O93" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -3812,10 +4220,12 @@
       <c r="I94" s="9" t="n"/>
       <c r="J94" s="9" t="n"/>
       <c r="K94" s="9" t="n"/>
-      <c r="L94" s="10" t="n">
+      <c r="L94" s="9" t="n"/>
+      <c r="M94" s="9" t="n"/>
+      <c r="N94" s="10" t="n">
         <v>21075</v>
       </c>
-      <c r="M94" s="9" t="n"/>
+      <c r="O94" s="9" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -3835,6 +4245,8 @@
       <c r="K95" s="5" t="n"/>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="5" t="n"/>
+      <c r="N95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -3855,7 +4267,7 @@
         <v>1543</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1543</v>
@@ -3867,15 +4279,21 @@
         <v>33.3</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>39</v>
+        <v>44.5</v>
       </c>
       <c r="K96" s="7" t="n">
-        <v>149</v>
-      </c>
-      <c r="L96" s="7" t="n">
-        <v>95325</v>
-      </c>
-      <c r="M96" s="6" t="inlineStr">
+        <v>49</v>
+      </c>
+      <c r="L96" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="M96" s="7" t="n">
+        <v>178</v>
+      </c>
+      <c r="N96" s="7" t="n">
+        <v>114141</v>
+      </c>
+      <c r="O96" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -3900,27 +4318,33 @@
         <v>1699</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>1785</v>
+        <v>1745</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>1190</v>
+        <v>1164</v>
       </c>
       <c r="I97" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J97" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="L97" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K97" s="12" t="n">
+      <c r="M97" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="L97" s="12" t="n">
+      <c r="N97" s="12" t="n">
         <v>59279</v>
       </c>
-      <c r="M97" s="11" t="inlineStr">
+      <c r="O97" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -3945,27 +4369,33 @@
         <v>1387</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1558</v>
+        <v>1485</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>1040</v>
+        <v>990</v>
       </c>
       <c r="I98" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J98" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L98" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K98" s="12" t="n">
+      <c r="M98" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="L98" s="12" t="n">
+      <c r="N98" s="12" t="n">
         <v>19444</v>
       </c>
-      <c r="M98" s="11" t="inlineStr">
+      <c r="O98" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -3990,74 +4420,86 @@
         <v>2010</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>2117</v>
+        <v>2090</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>1412</v>
+        <v>1394</v>
       </c>
       <c r="I99" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J99" s="11" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="L99" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="M99" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="N99" s="12" t="n">
         <v>15787</v>
       </c>
-      <c r="M99" s="11" t="inlineStr">
+      <c r="O99" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тонизирующие гидрогелевые патчи для глаз с экстрактом какао</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n">
+      <c r="B100" s="6" t="n">
         <v>179611304</v>
       </c>
-      <c r="C100" s="12" t="n">
+      <c r="C100" s="7" t="n">
         <v>415</v>
       </c>
-      <c r="D100" s="11" t="n">
+      <c r="D100" s="6" t="n">
         <v>144</v>
       </c>
-      <c r="E100" s="12" t="n">
+      <c r="E100" s="7" t="n">
         <v>1543</v>
       </c>
-      <c r="F100" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>1558</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>1040</v>
-      </c>
-      <c r="I100" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J100" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>125</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>17948</v>
-      </c>
-      <c r="M100" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F100" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J100" s="6" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="L100" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="M100" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="N100" s="7" t="n">
+        <v>19449</v>
+      </c>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -4080,27 +4522,33 @@
         <v>1699</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>1785</v>
+        <v>1718</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>1190</v>
+        <v>1146</v>
       </c>
       <c r="I101" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J101" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L101" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K101" s="12" t="n">
+      <c r="M101" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="L101" s="12" t="n">
+      <c r="N101" s="12" t="n">
         <v>29493</v>
       </c>
-      <c r="M101" s="11" t="inlineStr">
+      <c r="O101" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4125,27 +4573,33 @@
         <v>1387</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1470</v>
+        <v>1407</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>981</v>
+        <v>939</v>
       </c>
       <c r="I102" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J102" s="11" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="L102" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K102" s="12" t="n">
+      <c r="M102" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="L102" s="12" t="n">
+      <c r="N102" s="12" t="n">
         <v>63849</v>
       </c>
-      <c r="M102" s="11" t="inlineStr">
+      <c r="O102" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4170,27 +4624,33 @@
         <v>1387</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>1558</v>
+        <v>1488</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>1040</v>
+        <v>993</v>
       </c>
       <c r="I103" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J103" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L103" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K103" s="12" t="n">
+      <c r="M103" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="L103" s="12" t="n">
+      <c r="N103" s="12" t="n">
         <v>62444</v>
       </c>
-      <c r="M103" s="11" t="inlineStr">
+      <c r="O103" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4215,74 +4675,86 @@
         <v>1232</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1558</v>
+        <v>1488</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1038</v>
+        <v>991</v>
       </c>
       <c r="I104" s="11" t="n">
         <v>33.4</v>
       </c>
       <c r="J104" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L104" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K104" s="12" t="n">
+      <c r="M104" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="L104" s="12" t="n">
+      <c r="N104" s="12" t="n">
         <v>75780</v>
       </c>
-      <c r="M104" s="11" t="inlineStr">
+      <c r="O104" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые патчи для глаз с золотом</t>
         </is>
       </c>
-      <c r="B105" s="11" t="n">
+      <c r="B105" s="6" t="n">
         <v>180711104</v>
       </c>
-      <c r="C105" s="12" t="n">
+      <c r="C105" s="7" t="n">
         <v>415</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="6" t="n">
         <v>405</v>
       </c>
-      <c r="E105" s="12" t="n">
+      <c r="E105" s="7" t="n">
         <v>1543</v>
       </c>
-      <c r="F105" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>1558</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>1040</v>
-      </c>
-      <c r="I105" s="11" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J105" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>125</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>50478</v>
-      </c>
-      <c r="M105" s="11" t="inlineStr">
-        <is>
-          <t>Поднять цену</t>
+      <c r="F105" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>1029</v>
+      </c>
+      <c r="I105" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K105" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L105" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="N105" s="7" t="n">
+        <v>61249</v>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>Оставлено (ROI≥30%)</t>
         </is>
       </c>
     </row>
@@ -4302,24 +4774,30 @@
       <c r="E106" s="12" t="n"/>
       <c r="F106" s="11" t="n"/>
       <c r="G106" s="12" t="n">
-        <v>465</v>
+        <v>391</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="I106" s="11" t="n">
         <v>33</v>
       </c>
       <c r="J106" s="11" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="L106" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K106" s="12" t="n">
+      <c r="M106" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L106" s="12" t="n">
+      <c r="N106" s="12" t="n">
         <v>6839</v>
       </c>
-      <c r="M106" s="11" t="inlineStr">
+      <c r="O106" s="11" t="inlineStr">
         <is>
           <t>Поднять до ROI30 (нет цены)</t>
         </is>
@@ -4341,24 +4819,30 @@
       <c r="E107" s="12" t="n"/>
       <c r="F107" s="11" t="n"/>
       <c r="G107" s="12" t="n">
-        <v>465</v>
+        <v>391</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="I107" s="11" t="n">
         <v>33</v>
       </c>
       <c r="J107" s="11" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="L107" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K107" s="12" t="n">
+      <c r="M107" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L107" s="12" t="n">
+      <c r="N107" s="12" t="n">
         <v>9147</v>
       </c>
-      <c r="M107" s="11" t="inlineStr">
+      <c r="O107" s="11" t="inlineStr">
         <is>
           <t>Поднять до ROI30 (нет цены)</t>
         </is>
@@ -4384,10 +4868,12 @@
       <c r="I108" s="9" t="n"/>
       <c r="J108" s="9" t="n"/>
       <c r="K108" s="9" t="n"/>
-      <c r="L108" s="10" t="n">
-        <v>505813</v>
-      </c>
+      <c r="L108" s="9" t="n"/>
       <c r="M108" s="9" t="n"/>
+      <c r="N108" s="10" t="n">
+        <v>536901</v>
+      </c>
+      <c r="O108" s="9" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -4407,6 +4893,8 @@
       <c r="K109" s="5" t="n"/>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="5" t="n"/>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
@@ -4430,24 +4918,30 @@
         <v>10</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="I110" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J110" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="L110" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K110" s="12" t="n">
+      <c r="M110" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="L110" s="12" t="n">
+      <c r="N110" s="12" t="n">
         <v>108129</v>
       </c>
-      <c r="M110" s="11" t="inlineStr">
+      <c r="O110" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4472,27 +4966,33 @@
         <v>1698</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1850</v>
+        <v>1802</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>1234</v>
+        <v>1202</v>
       </c>
       <c r="I111" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J111" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L111" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K111" s="12" t="n">
+      <c r="M111" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="L111" s="12" t="n">
+      <c r="N111" s="12" t="n">
         <v>80486</v>
       </c>
-      <c r="M111" s="11" t="inlineStr">
+      <c r="O111" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4517,27 +5017,33 @@
         <v>1543</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>1817</v>
+        <v>1738</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>1212</v>
+        <v>1159</v>
       </c>
       <c r="I112" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J112" s="11" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L112" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K112" s="12" t="n">
+      <c r="M112" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="L112" s="12" t="n">
+      <c r="N112" s="12" t="n">
         <v>59474</v>
       </c>
-      <c r="M112" s="11" t="inlineStr">
+      <c r="O112" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4562,7 +5068,7 @@
         <v>2010</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>2010</v>
@@ -4574,15 +5080,21 @@
         <v>33.3</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>45</v>
+        <v>44.4</v>
       </c>
       <c r="K113" s="7" t="n">
-        <v>226</v>
-      </c>
-      <c r="L113" s="7" t="n">
-        <v>74026</v>
-      </c>
-      <c r="M113" s="6" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="L113" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="M113" s="7" t="n">
+        <v>243</v>
+      </c>
+      <c r="N113" s="7" t="n">
+        <v>79336</v>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -4607,27 +5119,33 @@
         <v>1699</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>1758</v>
+        <v>1720</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>1172</v>
+        <v>1148</v>
       </c>
       <c r="I114" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J114" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K114" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="L114" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K114" s="12" t="n">
+      <c r="M114" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="L114" s="12" t="n">
+      <c r="N114" s="12" t="n">
         <v>39162</v>
       </c>
-      <c r="M114" s="11" t="inlineStr">
+      <c r="O114" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4652,27 +5170,33 @@
         <v>1543</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1757</v>
+        <v>1696</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>1170</v>
+        <v>1130</v>
       </c>
       <c r="I115" s="11" t="n">
         <v>33.4</v>
       </c>
       <c r="J115" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K115" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L115" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K115" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="L115" s="12" t="n">
+      <c r="N115" s="12" t="n">
         <v>41877</v>
       </c>
-      <c r="M115" s="11" t="inlineStr">
+      <c r="O115" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4697,27 +5221,33 @@
         <v>1499</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>1789</v>
+        <v>1747</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>1191</v>
+        <v>1164</v>
       </c>
       <c r="I116" s="11" t="n">
         <v>33.4</v>
       </c>
       <c r="J116" s="11" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K116" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="L116" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K116" s="12" t="n">
+      <c r="M116" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="L116" s="12" t="n">
+      <c r="N116" s="12" t="n">
         <v>14640</v>
       </c>
-      <c r="M116" s="11" t="inlineStr">
+      <c r="O116" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4742,27 +5272,33 @@
         <v>1511</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>2122</v>
+        <v>2064</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>1416</v>
+        <v>1376</v>
       </c>
       <c r="I117" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J117" s="11" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="L117" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K117" s="12" t="n">
+      <c r="M117" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="L117" s="12" t="n">
+      <c r="N117" s="12" t="n">
         <v>18857</v>
       </c>
-      <c r="M117" s="11" t="inlineStr">
+      <c r="O117" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4788,10 +5324,12 @@
       <c r="I118" s="9" t="n"/>
       <c r="J118" s="9" t="n"/>
       <c r="K118" s="9" t="n"/>
-      <c r="L118" s="10" t="n">
-        <v>436651</v>
-      </c>
+      <c r="L118" s="9" t="n"/>
       <c r="M118" s="9" t="n"/>
+      <c r="N118" s="10" t="n">
+        <v>441961</v>
+      </c>
+      <c r="O118" s="9" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -4811,6 +5349,8 @@
       <c r="K119" s="5" t="n"/>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="5" t="n"/>
+      <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
@@ -4831,27 +5371,33 @@
         <v>1699</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>1710</v>
+        <v>1767</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>1141</v>
+        <v>1178</v>
       </c>
       <c r="I120" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J120" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="K120" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="L120" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K120" s="12" t="n">
+      <c r="M120" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="L120" s="12" t="n">
+      <c r="N120" s="12" t="n">
         <v>764125</v>
       </c>
-      <c r="M120" s="11" t="inlineStr">
+      <c r="O120" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4876,27 +5422,33 @@
         <v>2946</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>3710</v>
+        <v>3702</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>2475</v>
+        <v>2469</v>
       </c>
       <c r="I121" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J121" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="L121" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K121" s="12" t="n">
+      <c r="M121" s="12" t="n">
         <v>328</v>
       </c>
-      <c r="L121" s="12" t="n">
+      <c r="N121" s="12" t="n">
         <v>33445</v>
       </c>
-      <c r="M121" s="11" t="inlineStr">
+      <c r="O121" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -4921,7 +5473,7 @@
         <v>2010</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>2010</v>
@@ -4933,15 +5485,21 @@
         <v>33.3</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>41</v>
+        <v>44.1</v>
       </c>
       <c r="K122" s="7" t="n">
-        <v>213</v>
-      </c>
-      <c r="L122" s="7" t="n">
-        <v>255330</v>
-      </c>
-      <c r="M122" s="6" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="L122" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="M122" s="7" t="n">
+        <v>239</v>
+      </c>
+      <c r="N122" s="7" t="n">
+        <v>287446</v>
+      </c>
+      <c r="O122" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -4966,27 +5524,33 @@
         <v>2323</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>2842</v>
+        <v>2834</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>1896</v>
+        <v>1890</v>
       </c>
       <c r="I123" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J123" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L123" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K123" s="12" t="n">
+      <c r="M123" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="L123" s="12" t="n">
+      <c r="N123" s="12" t="n">
         <v>1230</v>
       </c>
-      <c r="M123" s="11" t="inlineStr">
+      <c r="O123" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5011,7 +5575,7 @@
         <v>2262</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>2262</v>
@@ -5023,15 +5587,21 @@
         <v>33.3</v>
       </c>
       <c r="J124" s="6" t="n">
-        <v>71</v>
+        <v>44.3</v>
       </c>
       <c r="K124" s="7" t="n">
-        <v>343</v>
-      </c>
-      <c r="L124" s="7" t="n">
-        <v>275197</v>
-      </c>
-      <c r="M124" s="6" t="inlineStr">
+        <v>54</v>
+      </c>
+      <c r="L124" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="M124" s="7" t="n">
+        <v>369</v>
+      </c>
+      <c r="N124" s="7" t="n">
+        <v>296069</v>
+      </c>
+      <c r="O124" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5057,10 +5627,12 @@
       <c r="I125" s="9" t="n"/>
       <c r="J125" s="9" t="n"/>
       <c r="K125" s="9" t="n"/>
-      <c r="L125" s="10" t="n">
-        <v>1329327</v>
-      </c>
+      <c r="L125" s="9" t="n"/>
       <c r="M125" s="9" t="n"/>
+      <c r="N125" s="10" t="n">
+        <v>1382315</v>
+      </c>
+      <c r="O125" s="9" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -5080,6 +5652,8 @@
       <c r="K126" s="5" t="n"/>
       <c r="L126" s="5" t="n"/>
       <c r="M126" s="5" t="n"/>
+      <c r="N126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -5100,7 +5674,7 @@
         <v>2166</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>2166</v>
@@ -5112,15 +5686,21 @@
         <v>33.3</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>114</v>
+        <v>44.5</v>
       </c>
       <c r="K127" s="7" t="n">
-        <v>421</v>
-      </c>
-      <c r="L127" s="7" t="n">
-        <v>12626</v>
-      </c>
-      <c r="M127" s="6" t="inlineStr">
+        <v>46</v>
+      </c>
+      <c r="L127" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="M127" s="7" t="n">
+        <v>444</v>
+      </c>
+      <c r="N127" s="7" t="n">
+        <v>13330</v>
+      </c>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5145,7 +5725,7 @@
         <v>1543</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1543</v>
@@ -5157,15 +5737,21 @@
         <v>33.3</v>
       </c>
       <c r="J128" s="6" t="n">
-        <v>81</v>
+        <v>44.2</v>
       </c>
       <c r="K128" s="7" t="n">
-        <v>240</v>
-      </c>
-      <c r="L128" s="7" t="n">
-        <v>5271</v>
-      </c>
-      <c r="M128" s="6" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="L128" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="M128" s="7" t="n">
+        <v>267</v>
+      </c>
+      <c r="N128" s="7" t="n">
+        <v>5880</v>
+      </c>
+      <c r="O128" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5191,10 +5777,12 @@
       <c r="I129" s="9" t="n"/>
       <c r="J129" s="9" t="n"/>
       <c r="K129" s="9" t="n"/>
-      <c r="L129" s="10" t="n">
-        <v>17897</v>
-      </c>
+      <c r="L129" s="9" t="n"/>
       <c r="M129" s="9" t="n"/>
+      <c r="N129" s="10" t="n">
+        <v>19210</v>
+      </c>
+      <c r="O129" s="9" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -5214,6 +5802,8 @@
       <c r="K130" s="5" t="n"/>
       <c r="L130" s="5" t="n"/>
       <c r="M130" s="5" t="n"/>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
@@ -5234,27 +5824,33 @@
         <v>1854</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>1985</v>
+        <v>1930</v>
       </c>
       <c r="H131" s="12" t="n">
-        <v>1324</v>
+        <v>1287</v>
       </c>
       <c r="I131" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J131" s="11" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="K131" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L131" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K131" s="12" t="n">
+      <c r="M131" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="L131" s="12" t="n">
+      <c r="N131" s="12" t="n">
         <v>86579</v>
       </c>
-      <c r="M131" s="11" t="inlineStr">
+      <c r="O131" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5279,27 +5875,33 @@
         <v>3257</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>3597</v>
+        <v>3572</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>2399</v>
+        <v>2382</v>
       </c>
       <c r="I132" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J132" s="11" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="K132" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="L132" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K132" s="12" t="n">
+      <c r="M132" s="12" t="n">
         <v>317</v>
       </c>
-      <c r="L132" s="12" t="n">
+      <c r="N132" s="12" t="n">
         <v>17444</v>
       </c>
-      <c r="M132" s="11" t="inlineStr">
+      <c r="O132" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5325,10 +5927,12 @@
       <c r="I133" s="9" t="n"/>
       <c r="J133" s="9" t="n"/>
       <c r="K133" s="9" t="n"/>
-      <c r="L133" s="10" t="n">
+      <c r="L133" s="9" t="n"/>
+      <c r="M133" s="9" t="n"/>
+      <c r="N133" s="10" t="n">
         <v>104023</v>
       </c>
-      <c r="M133" s="9" t="n"/>
+      <c r="O133" s="9" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -5348,6 +5952,8 @@
       <c r="K134" s="5" t="n"/>
       <c r="L134" s="5" t="n"/>
       <c r="M134" s="5" t="n"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
@@ -5368,27 +5974,33 @@
         <v>2166</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>2532</v>
+        <v>2455</v>
       </c>
       <c r="H135" s="12" t="n">
-        <v>1689</v>
+        <v>1637</v>
       </c>
       <c r="I135" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J135" s="11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L135" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K135" s="12" t="n">
+      <c r="M135" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="L135" s="12" t="n">
+      <c r="N135" s="12" t="n">
         <v>24910</v>
       </c>
-      <c r="M135" s="11" t="inlineStr">
+      <c r="O135" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5413,7 +6025,7 @@
         <v>2944</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>2944</v>
@@ -5425,15 +6037,21 @@
         <v>33.3</v>
       </c>
       <c r="J136" s="6" t="n">
-        <v>31</v>
+        <v>44.1</v>
       </c>
       <c r="K136" s="7" t="n">
-        <v>262</v>
-      </c>
-      <c r="L136" s="7" t="n">
-        <v>6543</v>
-      </c>
-      <c r="M136" s="6" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="L136" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="M136" s="7" t="n">
+        <v>278</v>
+      </c>
+      <c r="N136" s="7" t="n">
+        <v>6949</v>
+      </c>
+      <c r="O136" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5459,10 +6077,12 @@
       <c r="I137" s="9" t="n"/>
       <c r="J137" s="9" t="n"/>
       <c r="K137" s="9" t="n"/>
-      <c r="L137" s="10" t="n">
-        <v>31453</v>
-      </c>
+      <c r="L137" s="9" t="n"/>
       <c r="M137" s="9" t="n"/>
+      <c r="N137" s="10" t="n">
+        <v>31859</v>
+      </c>
+      <c r="O137" s="9" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -5482,6 +6102,8 @@
       <c r="K138" s="5" t="n"/>
       <c r="L138" s="5" t="n"/>
       <c r="M138" s="5" t="n"/>
+      <c r="N138" s="5" t="n"/>
+      <c r="O138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
@@ -5502,27 +6124,33 @@
         <v>2280</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>2347</v>
+        <v>2377</v>
       </c>
       <c r="H139" s="12" t="n">
-        <v>1566</v>
+        <v>1586</v>
       </c>
       <c r="I139" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J139" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K139" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L139" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K139" s="12" t="n">
+      <c r="M139" s="12" t="n">
         <v>199</v>
       </c>
-      <c r="L139" s="12" t="n">
+      <c r="N139" s="12" t="n">
         <v>3182545</v>
       </c>
-      <c r="M139" s="11" t="inlineStr">
+      <c r="O139" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5547,27 +6175,33 @@
         <v>1698</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>1866</v>
+        <v>1780</v>
       </c>
       <c r="H140" s="12" t="n">
-        <v>1244</v>
+        <v>1187</v>
       </c>
       <c r="I140" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J140" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K140" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L140" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K140" s="12" t="n">
+      <c r="M140" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="L140" s="12" t="n">
+      <c r="N140" s="12" t="n">
         <v>1341092</v>
       </c>
-      <c r="M140" s="11" t="inlineStr">
+      <c r="O140" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5592,7 +6226,7 @@
         <v>2166</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>2166</v>
@@ -5604,15 +6238,21 @@
         <v>33.3</v>
       </c>
       <c r="J141" s="6" t="n">
-        <v>48</v>
+        <v>44.6</v>
       </c>
       <c r="K141" s="7" t="n">
-        <v>257</v>
-      </c>
-      <c r="L141" s="7" t="n">
-        <v>569044</v>
-      </c>
-      <c r="M141" s="6" t="inlineStr">
+        <v>44</v>
+      </c>
+      <c r="L141" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="M141" s="7" t="n">
+        <v>291</v>
+      </c>
+      <c r="N141" s="7" t="n">
+        <v>646033</v>
+      </c>
+      <c r="O141" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5637,7 +6277,7 @@
         <v>610</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>610</v>
@@ -5649,15 +6289,21 @@
         <v>33.5</v>
       </c>
       <c r="J142" s="6" t="n">
-        <v>57</v>
+        <v>44.1</v>
       </c>
       <c r="K142" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L142" s="7" t="n">
-        <v>71217</v>
-      </c>
-      <c r="M142" s="6" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="L142" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="M142" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="N142" s="7" t="n">
+        <v>135963</v>
+      </c>
+      <c r="O142" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5682,7 +6328,7 @@
         <v>2789</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G143" s="7" t="n">
         <v>2789</v>
@@ -5694,15 +6340,21 @@
         <v>33.3</v>
       </c>
       <c r="J143" s="6" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K143" s="7" t="n">
-        <v>420</v>
-      </c>
-      <c r="L143" s="7" t="n">
-        <v>5465</v>
-      </c>
-      <c r="M143" s="6" t="inlineStr">
+        <v>61</v>
+      </c>
+      <c r="L143" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="M143" s="7" t="n">
+        <v>463</v>
+      </c>
+      <c r="N143" s="7" t="n">
+        <v>6020</v>
+      </c>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5727,27 +6379,33 @@
         <v>2944</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>2983</v>
+        <v>2949</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1990</v>
+        <v>1967</v>
       </c>
       <c r="I144" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J144" s="11" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="K144" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="L144" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K144" s="12" t="n">
+      <c r="M144" s="12" t="n">
         <v>259</v>
       </c>
-      <c r="L144" s="12" t="n">
+      <c r="N144" s="12" t="n">
         <v>91509</v>
       </c>
-      <c r="M144" s="11" t="inlineStr">
+      <c r="O144" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5772,27 +6430,33 @@
         <v>2323</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>2487</v>
+        <v>2428</v>
       </c>
       <c r="H145" s="12" t="n">
-        <v>1659</v>
+        <v>1620</v>
       </c>
       <c r="I145" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J145" s="11" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="K145" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L145" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K145" s="12" t="n">
+      <c r="M145" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="L145" s="12" t="n">
+      <c r="N145" s="12" t="n">
         <v>309202</v>
       </c>
-      <c r="M145" s="11" t="inlineStr">
+      <c r="O145" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5817,27 +6481,33 @@
         <v>2478</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>2665</v>
+        <v>2640</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>1777</v>
+        <v>1761</v>
       </c>
       <c r="I146" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J146" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="K146" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L146" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K146" s="12" t="n">
+      <c r="M146" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="L146" s="12" t="n">
+      <c r="N146" s="12" t="n">
         <v>8020</v>
       </c>
-      <c r="M146" s="11" t="inlineStr">
+      <c r="O146" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5862,7 +6532,7 @@
         <v>2167</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>2167</v>
@@ -5874,15 +6544,21 @@
         <v>33.3</v>
       </c>
       <c r="J147" s="6" t="n">
-        <v>42</v>
+        <v>44.2</v>
       </c>
       <c r="K147" s="7" t="n">
-        <v>233</v>
-      </c>
-      <c r="L147" s="7" t="n">
-        <v>320378</v>
-      </c>
-      <c r="M147" s="6" t="inlineStr">
+        <v>62</v>
+      </c>
+      <c r="L147" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="M147" s="7" t="n">
+        <v>255</v>
+      </c>
+      <c r="N147" s="7" t="n">
+        <v>350172</v>
+      </c>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5907,7 +6583,7 @@
         <v>2634</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>2634</v>
@@ -5919,15 +6595,21 @@
         <v>33.3</v>
       </c>
       <c r="J148" s="6" t="n">
-        <v>43</v>
+        <v>44.3</v>
       </c>
       <c r="K148" s="7" t="n">
-        <v>293</v>
-      </c>
-      <c r="L148" s="7" t="n">
-        <v>22542</v>
-      </c>
-      <c r="M148" s="6" t="inlineStr">
+        <v>62</v>
+      </c>
+      <c r="L148" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="M148" s="7" t="n">
+        <v>308</v>
+      </c>
+      <c r="N148" s="7" t="n">
+        <v>23701</v>
+      </c>
+      <c r="O148" s="6" t="inlineStr">
         <is>
           <t>Оставлено (ROI≥30%)</t>
         </is>
@@ -5952,27 +6634,33 @@
         <v>2479</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>2524</v>
+        <v>2515</v>
       </c>
       <c r="H149" s="12" t="n">
-        <v>1684</v>
+        <v>1678</v>
       </c>
       <c r="I149" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J149" s="11" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K149" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="L149" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K149" s="12" t="n">
+      <c r="M149" s="12" t="n">
         <v>216</v>
       </c>
-      <c r="L149" s="12" t="n">
+      <c r="N149" s="12" t="n">
         <v>5181</v>
       </c>
-      <c r="M149" s="11" t="inlineStr">
+      <c r="O149" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -5998,10 +6686,12 @@
       <c r="I150" s="9" t="n"/>
       <c r="J150" s="9" t="n"/>
       <c r="K150" s="9" t="n"/>
-      <c r="L150" s="10" t="n">
-        <v>5926195</v>
-      </c>
+      <c r="L150" s="9" t="n"/>
       <c r="M150" s="9" t="n"/>
+      <c r="N150" s="10" t="n">
+        <v>6099438</v>
+      </c>
+      <c r="O150" s="9" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -6021,6 +6711,8 @@
       <c r="K151" s="5" t="n"/>
       <c r="L151" s="5" t="n"/>
       <c r="M151" s="5" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
@@ -6041,27 +6733,33 @@
         <v>3591</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>4482</v>
+        <v>4443</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>2989</v>
+        <v>2964</v>
       </c>
       <c r="I152" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J152" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K152" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="L152" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K152" s="12" t="n">
+      <c r="M152" s="12" t="n">
         <v>401</v>
       </c>
-      <c r="L152" s="12" t="n">
+      <c r="N152" s="12" t="n">
         <v>403991</v>
       </c>
-      <c r="M152" s="11" t="inlineStr">
+      <c r="O152" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -6086,27 +6784,33 @@
         <v>2241</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>3333</v>
+        <v>3221</v>
       </c>
       <c r="H153" s="12" t="n">
-        <v>2223</v>
+        <v>2148</v>
       </c>
       <c r="I153" s="11" t="n">
         <v>33.3</v>
       </c>
       <c r="J153" s="11" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K153" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="L153" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="K153" s="12" t="n">
+      <c r="M153" s="12" t="n">
         <v>292</v>
       </c>
-      <c r="L153" s="12" t="n">
+      <c r="N153" s="12" t="n">
         <v>116008</v>
       </c>
-      <c r="M153" s="11" t="inlineStr">
+      <c r="O153" s="11" t="inlineStr">
         <is>
           <t>Поднять цену</t>
         </is>
@@ -6132,10 +6836,12 @@
       <c r="I154" s="9" t="n"/>
       <c r="J154" s="9" t="n"/>
       <c r="K154" s="9" t="n"/>
-      <c r="L154" s="10" t="n">
+      <c r="L154" s="9" t="n"/>
+      <c r="M154" s="9" t="n"/>
+      <c r="N154" s="10" t="n">
         <v>519999</v>
       </c>
-      <c r="M154" s="9" t="n"/>
+      <c r="O154" s="9" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
@@ -6157,15 +6863,17 @@
       <c r="I156" s="14" t="n"/>
       <c r="J156" s="14" t="n"/>
       <c r="K156" s="14" t="n"/>
-      <c r="L156" s="15" t="n">
-        <v>19324404</v>
-      </c>
+      <c r="L156" s="14" t="n"/>
       <c r="M156" s="14" t="n"/>
+      <c r="N156" s="15" t="n">
+        <v>20831444</v>
+      </c>
+      <c r="O156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="16" t="inlineStr">
         <is>
-          <t>Себес остатков: 47.46 млн ₽  |  Заработок при ROI≥30%: 19.32 млн ₽  |  Остаток: 107,901 шт  |  Поднять цену: 47 из 99</t>
+          <t>Себес: 47.46 млн ₽ | Заработок ROI≥30%: 20.83 млн ₽ | Остаток: 107,901 шт | Поднять цену: 36 из 99 | Ставки-факт: 96</t>
         </is>
       </c>
     </row>
